--- a/data/trans_orig/P37C3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son efectivas en 2023</t>
+          <t>Población según la creencia de que las vacunas son efectivas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>863</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>33049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>275015</t>
+          <t>273716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>295660</t>
+          <t>295585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264410</t>
+          <t>264213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277268</t>
+          <t>276492</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>544828</t>
+          <t>545120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568983</t>
+          <t>569777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>21262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50851</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39582</t>
+          <t>38813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69386</t>
+          <t>72746</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148399</t>
+          <t>147542</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205977</t>
+          <t>205666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129271</t>
+          <t>127222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166758</t>
+          <t>164471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286346</t>
+          <t>289301</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>355312</t>
+          <t>356201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278799</t>
+          <t>274959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334331</t>
+          <t>335330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>323770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359962</t>
+          <t>362919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>617620</t>
+          <t>611886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>688679</t>
+          <t>681541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>21170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40774</t>
+          <t>42518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34404</t>
+          <t>34800</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41812</t>
+          <t>42008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70110</t>
+          <t>69470</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256275</t>
+          <t>254554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281122</t>
+          <t>281417</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290441</t>
+          <t>289435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310822</t>
+          <t>310365</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>554023</t>
+          <t>553797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>586602</t>
+          <t>586245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -2776,82 +2776,82 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3076</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2889,97 +2889,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2254</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>419</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2211</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35375</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277650</t>
+          <t>277095</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>296288</t>
+          <t>296479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>444240</t>
+          <t>447617</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>466623</t>
+          <t>466300</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>733791</t>
+          <t>734227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>760086</t>
+          <t>760783</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -3458,97 +3458,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18496</t>
+          <t>19502</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>94545</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>117347</t>
+          <t>115675</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>145610</t>
+          <t>143783</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>163129</t>
+          <t>162274</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>245663</t>
+          <t>244777</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>273748</t>
+          <t>274208</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>70538</t>
+          <t>69647</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39707</t>
+          <t>40022</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>56657</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93561</t>
+          <t>94123</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121497</t>
+          <t>121097</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>456</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18858</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18800</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39338</t>
+          <t>38898</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>64619</t>
+          <t>64077</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>67117</t>
+          <t>65251</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>98485</t>
+          <t>97792</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>179825</t>
+          <t>180488</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>208282</t>
+          <t>208132</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>199295</t>
+          <t>199729</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>219676</t>
+          <t>220757</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>386411</t>
+          <t>385381</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>422283</t>
+          <t>420593</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>19857</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>65432</t>
+          <t>63953</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>72094</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>59230</t>
+          <t>62438</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>123429</t>
+          <t>123549</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>135715</t>
+          <t>135215</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>186563</t>
+          <t>187473</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>67625</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>199240</t>
+          <t>200653</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>196055</t>
+          <t>202004</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>367874</t>
+          <t>368323</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>372783</t>
+          <t>374654</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>428962</t>
+          <t>431196</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>559543</t>
+          <t>561020</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>750174</t>
+          <t>739720</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>950171</t>
+          <t>955608</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1184948</t>
+          <t>1179431</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -5504,82 +5504,82 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>2336</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>3279</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>24127</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>19628</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>62275</t>
+          <t>65428</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>55842</t>
+          <t>51812</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>45298</t>
+          <t>45719</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>99584</t>
+          <t>100359</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>85593</t>
+          <t>78495</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>273374</t>
+          <t>278825</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>147935</t>
+          <t>147604</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>187028</t>
+          <t>187011</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>218249</t>
+          <t>218883</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>438842</t>
+          <t>437905</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>581377</t>
+          <t>577442</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>815874</t>
+          <t>826626</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>488174</t>
+          <t>488243</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>531041</t>
+          <t>531299</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1098164</t>
+          <t>1095000</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1371487</t>
+          <t>1373627</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>32959</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>70136</t>
+          <t>69553</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>132818</t>
+          <t>132856</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>205386</t>
+          <t>207348</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>109619</t>
+          <t>111912</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>168865</t>
+          <t>169206</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>265628</t>
+          <t>261405</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>358573</t>
+          <t>354722</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>557138</t>
+          <t>554366</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>807825</t>
+          <t>804524</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>559535</t>
+          <t>570025</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>752243</t>
+          <t>754026</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1232914</t>
+          <t>1207697</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1531337</t>
+          <t>1522007</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2396887</t>
+          <t>2399194</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2717496</t>
+          <t>2703046</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2701033</t>
+          <t>2701061</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2930938</t>
+          <t>2928813</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5135309</t>
+          <t>5141782</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5519165</t>
+          <t>5538950</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37C3_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>668</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>962</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33049</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>287147</t>
+          <t>295154</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273716</t>
+          <t>284463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>295585</t>
+          <t>302949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>271796</t>
+          <t>296925</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264213</t>
+          <t>290575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>276492</t>
+          <t>302585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>558943</t>
+          <t>592080</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545120</t>
+          <t>578726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>569777</t>
+          <t>601804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>309885</t>
+          <t>317609</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>309885</t>
+          <t>317609</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>309885</t>
+          <t>317609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289142</t>
+          <t>315574</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289142</t>
+          <t>315574</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289142</t>
+          <t>315574</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,49 +1452,49 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7938</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2778</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>8602</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,05%</t>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32882</t>
+          <t>32545</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>47660</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>51810</t>
+          <t>53150</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38813</t>
+          <t>39920</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72746</t>
+          <t>70032</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>175939</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147542</t>
+          <t>155625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205666</t>
+          <t>210620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>146061</t>
+          <t>155092</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127222</t>
+          <t>135485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164471</t>
+          <t>173090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>335518</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>289301</t>
+          <t>303476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>356201</t>
+          <t>365659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>307076</t>
+          <t>315264</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274959</t>
+          <t>284089</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335330</t>
+          <t>342167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>342892</t>
+          <t>363268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323770</t>
+          <t>344055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362919</t>
+          <t>382990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>649968</t>
+          <t>678532</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>611886</t>
+          <t>644445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>681541</t>
+          <t>713141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>563</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21170</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>25379</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>28237</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42518</t>
+          <t>39080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25067</t>
+          <t>25163</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>53872</t>
+          <t>53401</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69470</t>
+          <t>67234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>270080</t>
+          <t>268893</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254554</t>
+          <t>254438</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281417</t>
+          <t>280472</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>301760</t>
+          <t>309188</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>289435</t>
+          <t>298098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310365</t>
+          <t>318498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>571839</t>
+          <t>578081</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>553797</t>
+          <t>561522</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>586245</t>
+          <t>594830</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>342017</t>
+          <t>351344</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>342017</t>
+          <t>351344</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>342017</t>
+          <t>351344</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>657062</t>
+          <t>666403</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>657062</t>
+          <t>666403</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>657062</t>
+          <t>666403</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>470</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>470</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16682</t>
+          <t>27536</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>48989</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>290152</t>
+          <t>333449</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277095</t>
+          <t>313956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>296479</t>
+          <t>342957</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>460587</t>
+          <t>404178</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>447617</t>
+          <t>391442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>466300</t>
+          <t>410329</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>750740</t>
+          <t>737628</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>734227</t>
+          <t>716402</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>760783</t>
+          <t>749434</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>105561</t>
+          <t>121663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94545</t>
+          <t>107946</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>115675</t>
+          <t>132349</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>154120</t>
+          <t>167313</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>143783</t>
+          <t>157360</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>162274</t>
+          <t>176345</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>259681</t>
+          <t>288976</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>244777</t>
+          <t>272761</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>274208</t>
+          <t>304827</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>59374</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>80734</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>47933</t>
+          <t>52190</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40022</t>
+          <t>44267</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58208</t>
+          <t>61643</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>107306</t>
+          <t>119310</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94123</t>
+          <t>104280</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121097</t>
+          <t>134573</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>611</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>369</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>26783</t>
+          <t>28685</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>39033</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>51131</t>
+          <t>52654</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>38898</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>64077</t>
+          <t>66619</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>24210</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>39986</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>81408</t>
+          <t>84779</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>65251</t>
+          <t>69517</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>97792</t>
+          <t>99558</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>194727</t>
+          <t>193943</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>180488</t>
+          <t>179497</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>208132</t>
+          <t>206828</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>210061</t>
+          <t>213986</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>199729</t>
+          <t>201397</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>220757</t>
+          <t>223129</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>404789</t>
+          <t>407929</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>385381</t>
+          <t>391868</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>420593</t>
+          <t>425631</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4827,57 +4827,57 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>7234</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>16423</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>6604</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>17544</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>54271</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>40551</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>63953</t>
+          <t>73282</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>49400</t>
+          <t>55198</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>40655</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>72094</t>
+          <t>72250</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>95901</t>
+          <t>109468</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>62438</t>
+          <t>90197</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>123549</t>
+          <t>136441</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>158750</t>
+          <t>187742</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>135215</t>
+          <t>160149</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>187473</t>
+          <t>216908</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>145672</t>
+          <t>174689</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>71865</t>
+          <t>154022</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>200653</t>
+          <t>195020</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>362432</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>202004</t>
+          <t>327572</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>368323</t>
+          <t>395231</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>402096</t>
+          <t>456444</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>374654</t>
+          <t>425298</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>431196</t>
+          <t>486106</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>636457</t>
+          <t>521686</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>561020</t>
+          <t>497497</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>739720</t>
+          <t>546617</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1038552</t>
+          <t>978132</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>955608</t>
+          <t>941266</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1179431</t>
+          <t>1017624</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>616179</t>
+          <t>709693</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>616179</t>
+          <t>709693</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>616179</t>
+          <t>709693</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>843063</t>
+          <t>764622</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>843063</t>
+          <t>764622</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>843063</t>
+          <t>764622</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1459242</t>
+          <t>1474316</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1459242</t>
+          <t>1474316</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1459242</t>
+          <t>1474316</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>688</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>688</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>24127</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>41731</t>
+          <t>50328</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>65428</t>
+          <t>65930</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>34443</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>45376</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>75313</t>
+          <t>84771</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>69043</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>100359</t>
+          <t>105769</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>196106</t>
+          <t>231545</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>78495</t>
+          <t>204157</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>278825</t>
+          <t>258574</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>166438</t>
+          <t>194281</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>147604</t>
+          <t>170618</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>187011</t>
+          <t>217694</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>362544</t>
+          <t>425826</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>218883</t>
+          <t>390177</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>437905</t>
+          <t>464738</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>678390</t>
+          <t>502159</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>577442</t>
+          <t>473134</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>826626</t>
+          <t>530450</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>510965</t>
+          <t>596919</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>488243</t>
+          <t>573877</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>531299</t>
+          <t>621477</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1189355</t>
+          <t>1099077</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1095000</t>
+          <t>1062540</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1373627</t>
+          <t>1134518</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>927177</t>
+          <t>796303</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>927177</t>
+          <t>796303</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>927177</t>
+          <t>796303</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1642569</t>
+          <t>1626911</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1642569</t>
+          <t>1626911</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1642569</t>
+          <t>1626911</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,102 +6181,102 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>12015</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>21796</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>13978</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>33947</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>11008</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>5785</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>21203</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>21410</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>12519</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>33850</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>38805</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>51797</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,67 +6329,67 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>61582</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>48062</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>78088</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>54540</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>41756</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>69553</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>171711</t>
+          <t>201650</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>132856</t>
+          <t>170487</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>207348</t>
+          <t>235387</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>139451</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>111912</t>
+          <t>130827</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>169206</t>
+          <t>177200</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>311163</t>
+          <t>354464</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>261405</t>
+          <t>320473</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>354722</t>
+          <t>396245</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>729351</t>
+          <t>814931</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>554366</t>
+          <t>758800</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>804524</t>
+          <t>873374</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>683939</t>
+          <t>766911</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>570025</t>
+          <t>726535</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>754026</t>
+          <t>812008</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1413290</t>
+          <t>1581842</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1207697</t>
+          <t>1511301</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1522007</t>
+          <t>1650635</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2489042</t>
+          <t>2432427</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2399194</t>
+          <t>2372909</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2703046</t>
+          <t>2494912</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2782451</t>
+          <t>2758340</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2701061</t>
+          <t>2711924</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2928813</t>
+          <t>2804954</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>5271493</t>
+          <t>5190767</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5141782</t>
+          <t>5114348</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5538950</t>
+          <t>5263986</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3433995</t>
+          <t>3497594</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3637900</t>
+          <t>3712857</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7071896</t>
+          <t>7210451</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
